--- a/CORRESPONSAL.xlsx
+++ b/CORRESPONSAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DADD76F6-EB70-443B-A889-FB72458CBBEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021C40FD-BCFC-493F-A483-A81347A68C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0A437848-A391-46C5-BDD4-FF220D880EC2}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0A437848-A391-46C5-BDD4-FF220D880EC2}"/>
   </bookViews>
   <sheets>
     <sheet name="CORRESPONSAL" sheetId="1" r:id="rId1"/>
@@ -24012,642 +24012,930 @@
       </c>
     </row>
     <row r="2630" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2630">
+        <v>43576520</v>
+      </c>
       <c r="B2630" t="str">
         <f t="shared" si="41"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2631" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2631">
+        <v>1082890773</v>
+      </c>
       <c r="B2631" t="str">
         <f t="shared" si="41"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2632" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2632">
+        <v>1131110175</v>
+      </c>
       <c r="B2632" t="str">
         <f t="shared" si="41"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2633" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2633">
+        <v>1050007541</v>
+      </c>
       <c r="B2633" t="str">
         <f t="shared" si="41"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2634" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2634">
+        <v>10777700</v>
+      </c>
       <c r="B2634" t="str">
         <f t="shared" si="41"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2635" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2635">
+        <v>64568121</v>
+      </c>
       <c r="B2635" t="str">
         <f t="shared" si="41"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2636" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2636">
+        <v>1063148418</v>
+      </c>
       <c r="B2636" t="str">
         <f t="shared" si="41"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2637" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2637">
+        <v>98552179</v>
+      </c>
       <c r="B2637" t="str">
         <f t="shared" si="41"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2638" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2638">
+        <v>50883633</v>
+      </c>
       <c r="B2638" t="str">
         <f t="shared" si="41"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2639" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2639">
+        <v>49716364</v>
+      </c>
       <c r="B2639" t="str">
         <f t="shared" si="41"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2640" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2640">
+        <v>1192900034</v>
+      </c>
       <c r="B2640" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2641" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2641" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2641">
+        <v>1007866679</v>
+      </c>
       <c r="B2641" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2642" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2642" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2642">
+        <v>1042442085</v>
+      </c>
       <c r="B2642" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2643" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2643" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2643">
+        <v>1002315433</v>
+      </c>
       <c r="B2643" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2644" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2644" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2644">
+        <v>39302367</v>
+      </c>
       <c r="B2644" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2645" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2645" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2645">
+        <v>1073824670</v>
+      </c>
       <c r="B2645" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2646" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2646" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2646">
+        <v>1096228392</v>
+      </c>
       <c r="B2646" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2647" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2647" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2647">
+        <v>1052970026</v>
+      </c>
       <c r="B2647" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2648" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2648" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2648">
+        <v>1043644492</v>
+      </c>
       <c r="B2648" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2649" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2649" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2649">
+        <v>33065996</v>
+      </c>
       <c r="B2649" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2650" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2650" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2650">
+        <v>39097842</v>
+      </c>
       <c r="B2650" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2651" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2651" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2651">
+        <v>1123560041</v>
+      </c>
       <c r="B2651" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2652" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2652" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2652">
+        <v>7937152</v>
+      </c>
       <c r="B2652" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2653" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2653" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2653">
+        <v>1137219141</v>
+      </c>
       <c r="B2653" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2654" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2654" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2654">
+        <v>1047443524</v>
+      </c>
       <c r="B2654" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2655" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2655" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2655">
+        <v>72225746</v>
+      </c>
       <c r="B2655" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2656" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2656" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2656">
+        <v>1068656120</v>
+      </c>
       <c r="B2656" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2657" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2657" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2657">
+        <v>49757108</v>
+      </c>
       <c r="B2657" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2658" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2658" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2658">
+        <v>26008023</v>
+      </c>
       <c r="B2658" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2659" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2659" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2659">
+        <v>45536491</v>
+      </c>
       <c r="B2659" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2660" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2660" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2660">
+        <v>1045722748</v>
+      </c>
       <c r="B2660" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2661" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2661" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2661">
+        <v>1095951397</v>
+      </c>
       <c r="B2661" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2662" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2662" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2662">
+        <v>1043849018</v>
+      </c>
       <c r="B2662" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2663" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2663" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2663">
+        <v>1003407048</v>
+      </c>
       <c r="B2663" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2664" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2664" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2664">
+        <v>91299007</v>
+      </c>
       <c r="B2664" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2665" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2665" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2665">
+        <v>9193319</v>
+      </c>
       <c r="B2665" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2666" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2666" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2666">
+        <v>92541768</v>
+      </c>
       <c r="B2666" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2667" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2667" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2667">
+        <v>77170645</v>
+      </c>
       <c r="B2667" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2668" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2668" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2668">
+        <v>1066718978</v>
+      </c>
       <c r="B2668" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2669" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2669" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2669">
+        <v>73210802</v>
+      </c>
       <c r="B2669" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2670" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2670" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2670">
+        <v>1003044343</v>
+      </c>
       <c r="B2670" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2671" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2671" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2671">
+        <v>1035642052</v>
+      </c>
       <c r="B2671" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2672" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2672" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2672">
+        <v>1100546087</v>
+      </c>
       <c r="B2672" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2673" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2673" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2673">
+        <v>1095918369</v>
+      </c>
       <c r="B2673" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2674" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2674" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2674">
+        <v>1003246579</v>
+      </c>
       <c r="B2674" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2675" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2675" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2675">
+        <v>78024759</v>
+      </c>
       <c r="B2675" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2676" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2676" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2676">
+        <v>64749006</v>
+      </c>
       <c r="B2676" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2677" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2677" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2677">
+        <v>1003498501</v>
+      </c>
       <c r="B2677" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2678" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2678" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2678">
+        <v>1073830170</v>
+      </c>
       <c r="B2678" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2679" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2679" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2679">
+        <v>32612955</v>
+      </c>
       <c r="B2679" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2680" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2680" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2680">
+        <v>24718856</v>
+      </c>
       <c r="B2680" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2681" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2681" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2681">
+        <v>50918719</v>
+      </c>
       <c r="B2681" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2682" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2682" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2682">
+        <v>3809212</v>
+      </c>
       <c r="B2682" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2683" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2683" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2683">
+        <v>1068665562</v>
+      </c>
       <c r="B2683" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2684" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2684" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2684">
+        <v>1004501756</v>
+      </c>
       <c r="B2684" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2685" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2685" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2685">
+        <v>1003047781</v>
+      </c>
       <c r="B2685" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2686" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2686" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2686">
+        <v>1003002967</v>
+      </c>
       <c r="B2686" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2687" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2687" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2687">
+        <v>71971982</v>
+      </c>
       <c r="B2687" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2688" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2688" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2688">
+        <v>71331882</v>
+      </c>
       <c r="B2688" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2689" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2689" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2689">
+        <v>1050718112</v>
+      </c>
       <c r="B2689" t="str">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2690" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2690" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2690">
+        <v>9098812</v>
+      </c>
       <c r="B2690" t="str">
         <f t="shared" ref="B2690:B2753" si="42">+IF(A2690&lt;&gt;"","REINCIDENTE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="2691" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2691" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2691">
+        <v>1000872939</v>
+      </c>
       <c r="B2691" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2692" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2692" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2692">
+        <v>1005991158</v>
+      </c>
       <c r="B2692" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2693" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2693" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2693">
+        <v>8473186</v>
+      </c>
       <c r="B2693" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2694" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2694" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2694">
+        <v>45527189</v>
+      </c>
       <c r="B2694" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2695" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2695" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2695">
+        <v>1063957693</v>
+      </c>
       <c r="B2695" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2696" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2696" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2696">
+        <v>1100332142</v>
+      </c>
       <c r="B2696" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2697" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2697" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2697">
+        <v>1048275115</v>
+      </c>
       <c r="B2697" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2698" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2698" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2698">
+        <v>1038092914</v>
+      </c>
       <c r="B2698" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2699" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2699" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2699">
+        <v>1098622327</v>
+      </c>
       <c r="B2699" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2700" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2700" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2700">
+        <v>1035234515</v>
+      </c>
       <c r="B2700" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2701" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2701" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2701">
+        <v>39276406</v>
+      </c>
       <c r="B2701" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2702" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2702" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2702">
+        <v>1100696722</v>
+      </c>
       <c r="B2702" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2703" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2703" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2703">
+        <v>1096186250</v>
+      </c>
       <c r="B2703" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2704" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2704" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2704">
+        <v>10937683</v>
+      </c>
       <c r="B2704" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2705" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2705" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2705">
+        <v>1000399635</v>
+      </c>
       <c r="B2705" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2706" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2706" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2706">
+        <v>64476837</v>
+      </c>
       <c r="B2706" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2707" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2707" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2707">
+        <v>1103950187</v>
+      </c>
       <c r="B2707" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2708" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2708" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2708">
+        <v>1047487672</v>
+      </c>
       <c r="B2708" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2709" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2709" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2709">
+        <v>1082883887</v>
+      </c>
       <c r="B2709" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2710" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2710" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2710">
+        <v>1102811704</v>
+      </c>
       <c r="B2710" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2711" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2711" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2711">
+        <v>8867799</v>
+      </c>
       <c r="B2711" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2712" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2712" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2712">
+        <v>1104013700</v>
+      </c>
       <c r="B2712" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2713" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2713" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2713">
+        <v>1067939942</v>
+      </c>
       <c r="B2713" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2714" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2714" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2714">
+        <v>1063590861</v>
+      </c>
       <c r="B2714" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2715" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2715" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2715">
+        <v>1066866747</v>
+      </c>
       <c r="B2715" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2716" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2716" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2716">
+        <v>1003718544</v>
+      </c>
       <c r="B2716" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2717" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2717" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2717">
+        <v>1067895148</v>
+      </c>
       <c r="B2717" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2718" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2718" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2718">
+        <v>1063646081</v>
+      </c>
       <c r="B2718" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2719" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2719" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2719">
+        <v>1065618096</v>
+      </c>
       <c r="B2719" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2720" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2720" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2720">
+        <v>1097303977</v>
+      </c>
       <c r="B2720" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2721" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2721" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2721">
+        <v>1103109416</v>
+      </c>
       <c r="B2721" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2722" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2722" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2722">
+        <v>1041976428</v>
+      </c>
       <c r="B2722" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2723" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2723" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2723">
+        <v>1098627794</v>
+      </c>
       <c r="B2723" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2724" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2724" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2724">
+        <v>1214467313</v>
+      </c>
       <c r="B2724" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2725" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2725" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2725">
+        <v>1073788342</v>
+      </c>
       <c r="B2725" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2726" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2726" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2726" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
     </row>
-    <row r="2727" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2727" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2727" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
     </row>
-    <row r="2728" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2728" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2728" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
     </row>
-    <row r="2729" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2729" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2729" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
     </row>
-    <row r="2730" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2730" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2730" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
     </row>
-    <row r="2731" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2731" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2731" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
     </row>
-    <row r="2732" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2732" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2732" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
     </row>
-    <row r="2733" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2733" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2733" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
     </row>
-    <row r="2734" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2734" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2734" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
     </row>
-    <row r="2735" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2735" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2735" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
     </row>
-    <row r="2736" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2736" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2736" t="str">
         <f t="shared" si="42"/>
         <v/>

--- a/CORRESPONSAL.xlsx
+++ b/CORRESPONSAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\APPSUPRE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021C40FD-BCFC-493F-A483-A81347A68C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B56130-B407-41C8-B453-C8752F7718FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0A437848-A391-46C5-BDD4-FF220D880EC2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0A437848-A391-46C5-BDD4-FF220D880EC2}"/>
   </bookViews>
   <sheets>
     <sheet name="CORRESPONSAL" sheetId="1" r:id="rId1"/>
@@ -24876,738 +24876,1068 @@
       </c>
     </row>
     <row r="2726" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2726">
+        <v>25785420</v>
+      </c>
       <c r="B2726" t="str">
         <f t="shared" si="42"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2727" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2727">
+        <v>1067963228</v>
+      </c>
       <c r="B2727" t="str">
         <f t="shared" si="42"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2728" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2728">
+        <v>50849480</v>
+      </c>
       <c r="B2728" t="str">
         <f t="shared" si="42"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2729" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2729">
+        <v>44156376</v>
+      </c>
       <c r="B2729" t="str">
         <f t="shared" si="42"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2730" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2730">
+        <v>73552513</v>
+      </c>
       <c r="B2730" t="str">
         <f t="shared" si="42"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2731" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2731">
+        <v>32857480</v>
+      </c>
       <c r="B2731" t="str">
         <f t="shared" si="42"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2732" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2732">
+        <v>1005441256</v>
+      </c>
       <c r="B2732" t="str">
         <f t="shared" si="42"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2733" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2733">
+        <v>1098286419</v>
+      </c>
       <c r="B2733" t="str">
         <f t="shared" si="42"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2734" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2734">
+        <v>43042601</v>
+      </c>
       <c r="B2734" t="str">
         <f t="shared" si="42"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2735" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2735">
+        <v>1026134938</v>
+      </c>
       <c r="B2735" t="str">
         <f t="shared" si="42"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2736" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2736">
+        <v>1102871029</v>
+      </c>
       <c r="B2736" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2737" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2737" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2737">
+        <v>91515295</v>
+      </c>
       <c r="B2737" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2738" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2738" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2738">
+        <v>1138024006</v>
+      </c>
       <c r="B2738" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2739" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2739" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2739">
+        <v>1194430309</v>
+      </c>
       <c r="B2739" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2740" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2740" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2740">
+        <v>15040197</v>
+      </c>
       <c r="B2740" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2741" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2741" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2741">
+        <v>1103740430</v>
+      </c>
       <c r="B2741" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2742" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2742" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2742">
+        <v>1043973335</v>
+      </c>
       <c r="B2742" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2743" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2743" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2743">
+        <v>49722111</v>
+      </c>
       <c r="B2743" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2744" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2744" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2744">
+        <v>1067927921</v>
+      </c>
       <c r="B2744" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2745" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2745" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2745">
+        <v>1102794066</v>
+      </c>
       <c r="B2745" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2746" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2746" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2746">
+        <v>1020404296</v>
+      </c>
       <c r="B2746" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2747" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2747" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2747">
+        <v>1099367482</v>
+      </c>
       <c r="B2747" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2748" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2748" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2748">
+        <v>1001741335</v>
+      </c>
       <c r="B2748" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2749" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2749" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2749">
+        <v>1043668463</v>
+      </c>
       <c r="B2749" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2750" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2750" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2750">
+        <v>1067869969</v>
+      </c>
       <c r="B2750" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2751" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2751" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2751">
+        <v>1051360785</v>
+      </c>
       <c r="B2751" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2752" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2752" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2752">
+        <v>30572207</v>
+      </c>
       <c r="B2752" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2753" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2753" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2753">
+        <v>1123400466</v>
+      </c>
       <c r="B2753" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2754" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2754" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2754">
+        <v>1124063711</v>
+      </c>
       <c r="B2754" t="str">
         <f t="shared" ref="B2754:B2817" si="43">+IF(A2754&lt;&gt;"","REINCIDENTE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="2755" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2755" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2755">
+        <v>1052970978</v>
+      </c>
       <c r="B2755" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2756" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2756" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2756">
+        <v>1069475344</v>
+      </c>
       <c r="B2756" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2757" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2757" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2757">
+        <v>1101455301</v>
+      </c>
       <c r="B2757" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2758" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2758" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2758">
+        <v>1067863686</v>
+      </c>
       <c r="B2758" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2759" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2759" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2759">
+        <v>78038164</v>
+      </c>
       <c r="B2759" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2760" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2760" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2760">
+        <v>1052994056</v>
+      </c>
       <c r="B2760" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2761" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2761" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2761">
+        <v>1096197613</v>
+      </c>
       <c r="B2761" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2762" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2762" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2762">
+        <v>42991952</v>
+      </c>
       <c r="B2762" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2763" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2763" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2763">
+        <v>71242177</v>
+      </c>
       <c r="B2763" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2764" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2764" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2764">
+        <v>1000974732</v>
+      </c>
       <c r="B2764" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2765" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2765" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2765">
+        <v>50894598</v>
+      </c>
       <c r="B2765" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2766" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2766" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2766">
+        <v>1007535855</v>
+      </c>
       <c r="B2766" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2767" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2767" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2767">
+        <v>1098642152</v>
+      </c>
       <c r="B2767" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2768" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2768" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2768">
+        <v>1000895514</v>
+      </c>
       <c r="B2768" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2769" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2769" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2769">
+        <v>1043613335</v>
+      </c>
       <c r="B2769" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2770" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2770" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2770">
+        <v>1005180555</v>
+      </c>
       <c r="B2770" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2771" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2771" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2771">
+        <v>1052961426</v>
+      </c>
       <c r="B2771" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2772" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2772" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2772">
+        <v>1002430972</v>
+      </c>
       <c r="B2772" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2773" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2773" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2773">
+        <v>1043017125</v>
+      </c>
       <c r="B2773" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2774" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2774" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2774">
+        <v>1102233628</v>
+      </c>
       <c r="B2774" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2775" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2775" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2775">
+        <v>1047490838</v>
+      </c>
       <c r="B2775" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2776" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2776" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2776">
+        <v>92554438</v>
+      </c>
       <c r="B2776" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2777" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2777" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2777">
+        <v>1002501058</v>
+      </c>
       <c r="B2777" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2778" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2778" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2778">
+        <v>22443022</v>
+      </c>
       <c r="B2778" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2779" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2779" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2779">
+        <v>1098746615</v>
+      </c>
       <c r="B2779" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2780" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2780" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2780">
+        <v>1073989530</v>
+      </c>
       <c r="B2780" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2781" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2781" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2781">
+        <v>42203293</v>
+      </c>
       <c r="B2781" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2782" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2782" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2782">
+        <v>1081800874</v>
+      </c>
       <c r="B2782" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2783" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2783" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2783">
+        <v>1052990060</v>
+      </c>
       <c r="B2783" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2784" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2784" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2784">
+        <v>1002999070</v>
+      </c>
       <c r="B2784" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2785" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2785" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2785">
+        <v>1040492411</v>
+      </c>
       <c r="B2785" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2786" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2786" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2786">
+        <v>1005178726</v>
+      </c>
       <c r="B2786" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2787" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2787" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2787">
+        <v>1102806240</v>
+      </c>
       <c r="B2787" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2788" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2788" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2788">
+        <v>1051443690</v>
+      </c>
       <c r="B2788" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2789" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2789" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2789">
+        <v>1143343507</v>
+      </c>
       <c r="B2789" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2790" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2790" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2790">
+        <v>71173289</v>
+      </c>
       <c r="B2790" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2791" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2791" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2791">
+        <v>1007553611</v>
+      </c>
       <c r="B2791" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2792" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2792" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2792">
+        <v>1034989975</v>
+      </c>
       <c r="B2792" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2793" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2793" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2793">
+        <v>3837707</v>
+      </c>
       <c r="B2793" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2794" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2794" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2794">
+        <v>1128426492</v>
+      </c>
       <c r="B2794" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2795" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2795" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2795">
+        <v>1063356255</v>
+      </c>
       <c r="B2795" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2796" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2796" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2796">
+        <v>23180843</v>
+      </c>
       <c r="B2796" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2797" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2797" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2797">
+        <v>22478418</v>
+      </c>
       <c r="B2797" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2798" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2798" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2798">
+        <v>1063153840</v>
+      </c>
       <c r="B2798" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2799" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2799" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2799">
+        <v>1052971173</v>
+      </c>
       <c r="B2799" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2800" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2800" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2800">
+        <v>22613283</v>
+      </c>
       <c r="B2800" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2801" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2801" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2801">
+        <v>1052995366</v>
+      </c>
       <c r="B2801" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2802" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2802" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2802">
+        <v>98702475</v>
+      </c>
       <c r="B2802" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2803" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2803" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2803">
+        <v>1047235735</v>
+      </c>
       <c r="B2803" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2804" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2804" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2804">
+        <v>8566186</v>
+      </c>
       <c r="B2804" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2805" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2805" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2805">
+        <v>1065859418</v>
+      </c>
       <c r="B2805" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2806" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2806" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2806">
+        <v>1043980388</v>
+      </c>
       <c r="B2806" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2807" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2807" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2807">
+        <v>1002431702</v>
+      </c>
       <c r="B2807" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2808" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2808" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2808">
+        <v>1103214317</v>
+      </c>
       <c r="B2808" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2809" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2809" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2809">
+        <v>1137524965</v>
+      </c>
       <c r="B2809" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2810" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2810" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2810">
+        <v>1193104776</v>
+      </c>
       <c r="B2810" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2811" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2811" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2811">
+        <v>13892929</v>
+      </c>
       <c r="B2811" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2812" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2812" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2812">
+        <v>63534502</v>
+      </c>
       <c r="B2812" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2813" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2813" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2813">
+        <v>78076284</v>
+      </c>
       <c r="B2813" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2814" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2814" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2814">
+        <v>1005331864</v>
+      </c>
       <c r="B2814" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2815" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2815" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2815">
+        <v>71384645</v>
+      </c>
       <c r="B2815" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2816" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2816" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2816">
+        <v>78754650</v>
+      </c>
       <c r="B2816" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2817" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2817" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2817">
+        <v>1041850442</v>
+      </c>
       <c r="B2817" t="str">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2818" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2818" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2818">
+        <v>50919850</v>
+      </c>
       <c r="B2818" t="str">
         <f t="shared" ref="B2818:B2881" si="44">+IF(A2818&lt;&gt;"","REINCIDENTE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="2819" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2819" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2819">
+        <v>36573787</v>
+      </c>
       <c r="B2819" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2820" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2820" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2820">
+        <v>73200691</v>
+      </c>
       <c r="B2820" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2821" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2821" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2821">
+        <v>1010086717</v>
+      </c>
       <c r="B2821" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2822" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2822" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2822">
+        <v>1102721905</v>
+      </c>
       <c r="B2822" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2823" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2823" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2823">
+        <v>1003589482</v>
+      </c>
       <c r="B2823" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2824" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2824" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2824">
+        <v>1042210333</v>
+      </c>
       <c r="B2824" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2825" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2825" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2825">
+        <v>1007792949</v>
+      </c>
       <c r="B2825" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2826" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2826" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2826">
+        <v>30653153</v>
+      </c>
       <c r="B2826" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2827" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2827" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2827">
+        <v>1143226730</v>
+      </c>
       <c r="B2827" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2828" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2828" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2828">
+        <v>1062959039</v>
+      </c>
       <c r="B2828" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2829" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2829" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2829">
+        <v>1000393764</v>
+      </c>
       <c r="B2829" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2830" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2830" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2830">
+        <v>64698794</v>
+      </c>
       <c r="B2830" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2831" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2831" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2831">
+        <v>1069738223</v>
+      </c>
       <c r="B2831" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2832" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2832" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2832">
+        <v>1003504888</v>
+      </c>
       <c r="B2832" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2833" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2833" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2833">
+        <v>1062429549</v>
+      </c>
       <c r="B2833" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2834" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2834" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2834">
+        <v>1038108651</v>
+      </c>
       <c r="B2834" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2835" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2835" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2835">
+        <v>1052974371</v>
+      </c>
       <c r="B2835" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2836" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2836" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2836" t="str">
         <f t="shared" si="44"/>
         <v/>
       </c>
     </row>
-    <row r="2837" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2837" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2837" t="str">
         <f t="shared" si="44"/>
         <v/>
       </c>
     </row>
-    <row r="2838" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2838" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2838" t="str">
         <f t="shared" si="44"/>
         <v/>
       </c>
     </row>
-    <row r="2839" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2839" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2839" t="str">
         <f t="shared" si="44"/>
         <v/>
       </c>
     </row>
-    <row r="2840" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2840" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2840" t="str">
         <f t="shared" si="44"/>
         <v/>
       </c>
     </row>
-    <row r="2841" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2841" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2841" t="str">
         <f t="shared" si="44"/>
         <v/>
       </c>
     </row>
-    <row r="2842" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2842" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2842" t="str">
         <f t="shared" si="44"/>
         <v/>
       </c>
     </row>
-    <row r="2843" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2843" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2843" t="str">
         <f t="shared" si="44"/>
         <v/>
       </c>
     </row>
-    <row r="2844" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2844" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2844" t="str">
         <f t="shared" si="44"/>
         <v/>
       </c>
     </row>
-    <row r="2845" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2845" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2845" t="str">
         <f t="shared" si="44"/>
         <v/>
       </c>
     </row>
-    <row r="2846" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2846" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2846" t="str">
         <f t="shared" si="44"/>
         <v/>
       </c>
     </row>
-    <row r="2847" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2847" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2847" t="str">
         <f t="shared" si="44"/>
         <v/>
       </c>
     </row>
-    <row r="2848" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2848" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2848" t="str">
         <f t="shared" si="44"/>
         <v/>

--- a/CORRESPONSAL.xlsx
+++ b/CORRESPONSAL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\APPSUPRE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B56130-B407-41C8-B453-C8752F7718FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B884816F-8350-4088-9F92-64FEC17BBC9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0A437848-A391-46C5-BDD4-FF220D880EC2}"/>
   </bookViews>
@@ -25866,558 +25866,831 @@
       </c>
     </row>
     <row r="2836" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2836">
+        <v>1050960514</v>
+      </c>
       <c r="B2836" t="str">
         <f t="shared" si="44"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2837" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2837">
+        <v>64477137</v>
+      </c>
       <c r="B2837" t="str">
         <f t="shared" si="44"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2838" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2838">
+        <v>77018062</v>
+      </c>
       <c r="B2838" t="str">
         <f t="shared" si="44"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2839" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2839">
+        <v>1005332962</v>
+      </c>
       <c r="B2839" t="str">
         <f t="shared" si="44"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2840" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2840">
+        <v>15042867</v>
+      </c>
       <c r="B2840" t="str">
         <f t="shared" si="44"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2841" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2841">
+        <v>1039690022</v>
+      </c>
       <c r="B2841" t="str">
         <f t="shared" si="44"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2842" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2842">
+        <v>28224050</v>
+      </c>
       <c r="B2842" t="str">
         <f t="shared" si="44"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2843" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2843">
+        <v>57272203</v>
+      </c>
       <c r="B2843" t="str">
         <f t="shared" si="44"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2844" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2844">
+        <v>36594953</v>
+      </c>
       <c r="B2844" t="str">
         <f t="shared" si="44"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2845" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2845">
+        <v>10010810</v>
+      </c>
       <c r="B2845" t="str">
         <f t="shared" si="44"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2846" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2846">
+        <v>52391228</v>
+      </c>
       <c r="B2846" t="str">
         <f t="shared" si="44"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2847" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2847">
+        <v>50927743</v>
+      </c>
       <c r="B2847" t="str">
         <f t="shared" si="44"/>
-        <v/>
+        <v>REINCIDENTE</v>
       </c>
     </row>
     <row r="2848" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2848">
+        <v>1101448823</v>
+      </c>
       <c r="B2848" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2849" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2849" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2849">
+        <v>1040497366</v>
+      </c>
       <c r="B2849" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2850" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2850" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2850">
+        <v>8708171</v>
+      </c>
       <c r="B2850" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2851" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2851" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2851">
+        <v>1010104660</v>
+      </c>
       <c r="B2851" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2852" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2852" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2852">
+        <v>1066511494</v>
+      </c>
       <c r="B2852" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2853" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2853" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2853">
+        <v>1028160344</v>
+      </c>
       <c r="B2853" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2854" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2854" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2854">
+        <v>34989506</v>
+      </c>
       <c r="B2854" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2855" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2855" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2855">
+        <v>1002128713</v>
+      </c>
       <c r="B2855" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2856" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2856" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2856">
+        <v>33311588</v>
+      </c>
       <c r="B2856" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2857" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2857" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2857">
+        <v>91428324</v>
+      </c>
       <c r="B2857" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2858" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2858" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2858">
+        <v>52461488</v>
+      </c>
       <c r="B2858" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2859" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2859" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2859">
+        <v>1042421295</v>
+      </c>
       <c r="B2859" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2860" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2860" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2860">
+        <v>1102835733</v>
+      </c>
       <c r="B2860" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2861" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2861" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2861">
+        <v>98614589</v>
+      </c>
       <c r="B2861" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2862" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2862" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2862">
+        <v>1005990554</v>
+      </c>
       <c r="B2862" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2863" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2863" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2863">
+        <v>1066865990</v>
+      </c>
       <c r="B2863" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2864" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2864" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2864">
+        <v>1232896344</v>
+      </c>
       <c r="B2864" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2865" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2865" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2865">
+        <v>1068589038</v>
+      </c>
       <c r="B2865" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2866" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2866" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2866">
+        <v>1062962309</v>
+      </c>
       <c r="B2866" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2867" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2867" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2867">
+        <v>73198655</v>
+      </c>
       <c r="B2867" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2868" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2868" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2868">
+        <v>1067596049</v>
+      </c>
       <c r="B2868" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2869" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2869" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2869">
+        <v>18777615</v>
+      </c>
       <c r="B2869" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2870" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2870" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2870">
+        <v>30878791</v>
+      </c>
       <c r="B2870" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2871" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2871" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2871">
+        <v>1082889261</v>
+      </c>
       <c r="B2871" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2872" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2872" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2872">
+        <v>1126239302</v>
+      </c>
       <c r="B2872" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2873" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2873" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2873">
+        <v>1232892576</v>
+      </c>
       <c r="B2873" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2874" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2874" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2874">
+        <v>7376955</v>
+      </c>
       <c r="B2874" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2875" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2875" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2875">
+        <v>1002244694</v>
+      </c>
       <c r="B2875" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2876" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2876" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2876">
+        <v>1065650864</v>
+      </c>
       <c r="B2876" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2877" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2877" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2877">
+        <v>1143404275</v>
+      </c>
       <c r="B2877" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2878" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2878" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2878">
+        <v>1007396229</v>
+      </c>
       <c r="B2878" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2879" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2879" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2879">
+        <v>73475714</v>
+      </c>
       <c r="B2879" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2880" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2880" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2880">
+        <v>50914770</v>
+      </c>
       <c r="B2880" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2881" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2881" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2881">
+        <v>9167516</v>
+      </c>
       <c r="B2881" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2882" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2882" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2882">
+        <v>1133774365</v>
+      </c>
       <c r="B2882" t="str">
         <f t="shared" ref="B2882:B2945" si="45">+IF(A2882&lt;&gt;"","REINCIDENTE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="2883" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2883" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2883">
+        <v>1099740244</v>
+      </c>
       <c r="B2883" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2884" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2884" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2884">
+        <v>1193321794</v>
+      </c>
       <c r="B2884" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2885" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2885" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2885">
+        <v>8799934</v>
+      </c>
       <c r="B2885" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2886" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2886" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2886">
+        <v>1152187335</v>
+      </c>
       <c r="B2886" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2887" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2887" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2887">
+        <v>1068662902</v>
+      </c>
       <c r="B2887" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2888" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2888" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2888">
+        <v>1067164410</v>
+      </c>
       <c r="B2888" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2889" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2889" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2889">
+        <v>1118567714</v>
+      </c>
       <c r="B2889" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2890" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2890" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2890">
+        <v>1118800711</v>
+      </c>
       <c r="B2890" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2891" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2891" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2891">
+        <v>1001610138</v>
+      </c>
       <c r="B2891" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2892" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2892" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2892">
+        <v>92450359</v>
+      </c>
       <c r="B2892" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2893" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2893" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2893">
+        <v>1067848302</v>
+      </c>
       <c r="B2893" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2894" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2894" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2894">
+        <v>1093801077</v>
+      </c>
       <c r="B2894" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2895" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2895" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2895">
+        <v>1043644546</v>
+      </c>
       <c r="B2895" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2896" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2896" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2896">
+        <v>1020451246</v>
+      </c>
       <c r="B2896" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2897" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2897" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2897">
+        <v>43837343</v>
+      </c>
       <c r="B2897" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2898" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2898" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2898">
+        <v>30579669</v>
+      </c>
       <c r="B2898" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2899" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2899" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2899">
+        <v>78075773</v>
+      </c>
       <c r="B2899" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2900" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2900" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2900">
+        <v>1014288207</v>
+      </c>
       <c r="B2900" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2901" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2901" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2901">
+        <v>1102370731</v>
+      </c>
       <c r="B2901" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2902" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2902" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2902">
+        <v>8104044</v>
+      </c>
       <c r="B2902" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2903" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2903" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2903">
+        <v>1069478803</v>
+      </c>
       <c r="B2903" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2904" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2904" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2904">
+        <v>1043141781</v>
+      </c>
       <c r="B2904" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2905" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2905" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2905">
+        <v>1192919435</v>
+      </c>
       <c r="B2905" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2906" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2906" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2906">
+        <v>1101884068</v>
+      </c>
       <c r="B2906" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2907" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2907" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2907">
+        <v>78695443</v>
+      </c>
       <c r="B2907" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2908" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2908" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2908">
+        <v>1131106550</v>
+      </c>
       <c r="B2908" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2909" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2909" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2909">
+        <v>1005441409</v>
+      </c>
       <c r="B2909" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2910" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2910" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2910">
+        <v>1007072153</v>
+      </c>
       <c r="B2910" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2911" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2911" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2911">
+        <v>1047482310</v>
+      </c>
       <c r="B2911" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2912" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2912" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2912">
+        <v>1005486519</v>
+      </c>
       <c r="B2912" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2913" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2913" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2913">
+        <v>50914166</v>
+      </c>
       <c r="B2913" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2914" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2914" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2914">
+        <v>1100891676</v>
+      </c>
       <c r="B2914" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2915" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2915" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2915">
+        <v>50570716</v>
+      </c>
       <c r="B2915" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2916" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2916" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2916">
+        <v>43702499</v>
+      </c>
       <c r="B2916" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2917" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2917" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2917">
+        <v>1007969488</v>
+      </c>
       <c r="B2917" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2918" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2918" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2918">
+        <v>10942601</v>
+      </c>
       <c r="B2918" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2919" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2919" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2919">
+        <v>1000536903</v>
+      </c>
       <c r="B2919" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2920" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2920" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2920">
+        <v>63297178</v>
+      </c>
       <c r="B2920" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2921" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2921" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2921">
+        <v>64721331</v>
+      </c>
       <c r="B2921" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2922" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2922" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2922">
+        <v>1007387936</v>
+      </c>
       <c r="B2922" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2923" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2923" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2923">
+        <v>1003139799</v>
+      </c>
       <c r="B2923" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2924" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2924" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2924">
+        <v>64720013</v>
+      </c>
       <c r="B2924" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2925" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2925" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2925">
+        <v>70731849</v>
+      </c>
       <c r="B2925" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2926" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2926" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2926">
+        <v>1027881612</v>
+      </c>
       <c r="B2926" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="2927" spans="2:2" x14ac:dyDescent="0.3">
+        <v>REINCIDENTE</v>
+      </c>
+    </row>
+    <row r="2927" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2927" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
-    <row r="2928" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2928" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2928" t="str">
         <f t="shared" si="45"/>
         <v/>
